--- a/Professional_Invoice_Template .xlsx
+++ b/Professional_Invoice_Template .xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
-    <t xml:space="preserve">[YOUR BUSINESS NAME]</t>
+    <t xml:space="preserve">[Your Business Name]</t>
   </si>
   <si>
     <t xml:space="preserve">INVOICE</t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">[DD/MM/YYYY]</t>
   </si>
   <si>
-    <t xml:space="preserve">[Phone]  •  [Email]</t>
+    <t xml:space="preserve">[Phone]  ·  [Email]</t>
   </si>
   <si>
     <t xml:space="preserve">DUE DATE</t>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">[Client Email / Phone]</t>
   </si>
   <si>
-    <t xml:space="preserve">DESCRIPTION</t>
+    <t xml:space="preserve">  DESCRIPTION</t>
   </si>
   <si>
     <t xml:space="preserve">QTY</t>
@@ -122,12 +122,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,8 +151,8 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="20"/>
-      <color rgb="FF0F172A"/>
+      <sz val="19"/>
+      <color rgb="FF0F1E33"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -161,36 +160,14 @@
     <font>
       <b val="true"/>
       <sz val="30"/>
-      <color rgb="FF2563EB"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0F172A"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF475569"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="8"/>
-      <color rgb="FF94A3B8"/>
+      <color rgb="FFC8A44D"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0F172A"/>
+      <color rgb="FF5A6B7D"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -198,7 +175,15 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF5A6B7D"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF0F1E33"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -206,30 +191,60 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF0F172A"/>
+      <color rgb="FFC8A44D"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF0F1E33"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF5A6B7D"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12.5"/>
+      <color rgb="FFC8A44D"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13.5"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF475569"/>
+      <color rgb="FF0F1E33"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF94A3B8"/>
+      <sz val="9.5"/>
+      <color rgb="FF5A6B7D"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -237,21 +252,22 @@
     <font>
       <b val="true"/>
       <i val="true"/>
-      <sz val="11"/>
-      <color rgb="FF2563EB"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF94A3B8"/>
+      <sz val="12"/>
+      <color rgb="FFC8A44D"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8.5"/>
+      <color rgb="FF5A6B7D"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,36 +276,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2563EB"/>
-        <bgColor rgb="FF0066CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0F172A"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor rgb="FF0F1E33"/>
+        <bgColor rgb="FF003300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF1F5F9"/>
+        <bgColor rgb="FFF7F9FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
+        <fgColor rgb="FFF7F9FC"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
-        <bgColor rgb="FFF1F5F9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -299,17 +303,44 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FF0F1E33"/>
       </left>
       <right style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FF0F1E33"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD8DEE7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD8DEE7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8DEE7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8DEE7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFC8A44D"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -338,7 +369,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -356,114 +387,106 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -496,12 +519,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF1F5F9"/>
-      <rgbColor rgb="FFE2E8F0"/>
+      <rgbColor rgb="FFF7F9FC"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD8DEE7"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -518,17 +541,17 @@
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF2563EB"/>
+      <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF475569"/>
-      <rgbColor rgb="FF94A3B8"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF5A6B7D"/>
+      <rgbColor rgb="FFC8A44D"/>
+      <rgbColor rgb="FF0F1E33"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF0F172A"/>
+      <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
@@ -717,28 +740,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:F41"/>
+  <dimension ref="B1:F43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="2.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="2"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="36.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -749,293 +772,352 @@
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="C6" s="4"/>
+      <c r="E6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="C7" s="4"/>
+      <c r="E7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="C8" s="4"/>
+      <c r="E8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10" t="s">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C17" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="14" t="s">
+      <c r="E17" s="11"/>
+      <c r="F17" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="18" t="str">
-        <f aca="false">IF(AND(C17&lt;&gt;"",D17&lt;&gt;""),C17*D17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="19"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="22" t="str">
+    <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15" t="str">
         <f aca="false">IF(AND(C18&lt;&gt;"",D18&lt;&gt;""),C18*D18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18" t="str">
+    <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="19" t="str">
         <f aca="false">IF(AND(C19&lt;&gt;"",D19&lt;&gt;""),C19*D19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="19"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="22" t="str">
+    <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="15" t="str">
         <f aca="false">IF(AND(C20&lt;&gt;"",D20&lt;&gt;""),C20*D20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="15"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18" t="str">
+    <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="16"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="19" t="str">
         <f aca="false">IF(AND(C21&lt;&gt;"",D21&lt;&gt;""),C21*D21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="19"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="22" t="str">
+    <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="12"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15" t="str">
         <f aca="false">IF(AND(C22&lt;&gt;"",D22&lt;&gt;""),C22*D22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="15"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18" t="str">
+    <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="16"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="19" t="str">
         <f aca="false">IF(AND(C23&lt;&gt;"",D23&lt;&gt;""),C23*D23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="19"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22" t="str">
+    <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="12"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="15" t="str">
         <f aca="false">IF(AND(C24&lt;&gt;"",D24&lt;&gt;""),C24*D24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18" t="str">
+    <row r="25" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="19" t="str">
         <f aca="false">IF(AND(C25&lt;&gt;"",D25&lt;&gt;""),C25*D25,"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="19"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="22" t="str">
+    <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="12"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="15" t="str">
         <f aca="false">IF(AND(C26&lt;&gt;"",D26&lt;&gt;""),C26*D26,"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="23" t="s">
+    <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="19" t="str">
+        <f aca="false">IF(AND(C27&lt;&gt;"",D27&lt;&gt;""),C27*D27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="15" t="str">
+        <f aca="false">IF(AND(C28&lt;&gt;"",D28&lt;&gt;""),C28*D28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="19" t="str">
+        <f aca="false">IF(AND(C29&lt;&gt;"",D29&lt;&gt;""),C29*D29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D31" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="23"/>
-      <c r="F28" s="24" t="n">
-        <f aca="false">SUM(F17:F26)</f>
+      <c r="E31" s="20"/>
+      <c r="F31" s="21" t="n">
+        <f aca="false">SUM(F18:F29)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="23" t="s">
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D32" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E29" s="23"/>
-      <c r="F29" s="24" t="n">
-        <f aca="false">F28*0.15</f>
+      <c r="E32" s="20"/>
+      <c r="F32" s="21" t="n">
+        <f aca="false">F31*0.15</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D30" s="25" t="s">
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D33" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="26" t="n">
-        <f aca="false">F28+F29</f>
+      <c r="E33" s="22"/>
+      <c r="F33" s="23" t="n">
+        <f aca="false">F31+F32</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8" t="s">
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="5" t="s">
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F36" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5" t="s">
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="24" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="5" t="s">
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="24" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="5" t="s">
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="24" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="29" t="s">
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+    </row>
+    <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-    </row>
-    <row r="40" customFormat="false" ht="1.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="31" t="s">
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="33">
     <mergeCell ref="B3:D4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D20:E20"/>
@@ -1045,16 +1127,23 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
     <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
